--- a/Results_experiment/exp_4/preds_1111113333322222.xlsx
+++ b/Results_experiment/exp_4/preds_1111113333322222.xlsx
@@ -990,7 +990,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D2">
-        <v>1.838146209716797</v>
+        <v>1.142408609390259</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1004,7 +1004,7 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>1.678274035453796</v>
+        <v>3.368241786956787</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1018,7 +1018,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D4">
-        <v>2.483778715133667</v>
+        <v>2.531249284744263</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1032,7 +1032,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D5">
-        <v>2.110904932022095</v>
+        <v>3.465794563293457</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1046,7 +1046,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D6">
-        <v>2.586848020553589</v>
+        <v>2.550243139266968</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1060,7 +1060,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>1.981359720230103</v>
+        <v>2.512470960617065</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1074,7 +1074,7 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>3.146728515625</v>
+        <v>3.950543403625488</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1088,7 +1088,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D9">
-        <v>8.595589637756348</v>
+        <v>11.82187557220459</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1102,7 +1102,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>2.91633415222168</v>
+        <v>2.861527919769287</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>2.5</v>
       </c>
       <c r="D11">
-        <v>2.758621215820312</v>
+        <v>2.907684803009033</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1130,7 +1130,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>2.819003582000732</v>
+        <v>2.751444578170776</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1144,7 +1144,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D13">
-        <v>2.51455020904541</v>
+        <v>2.893149137496948</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D14">
-        <v>1.66159725189209</v>
+        <v>2.406244039535522</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1172,7 +1172,7 @@
         <v>6.5</v>
       </c>
       <c r="D15">
-        <v>2.296667814254761</v>
+        <v>2.822328329086304</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D16">
-        <v>3.04955005645752</v>
+        <v>3.120800018310547</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D17">
-        <v>3.398050546646118</v>
+        <v>3.450535535812378</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1214,7 +1214,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D18">
-        <v>2.714721441268921</v>
+        <v>2.646046161651611</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1228,7 +1228,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D19">
-        <v>7.213894367218018</v>
+        <v>8.100494384765625</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D20">
-        <v>2.979333400726318</v>
+        <v>3.177014350891113</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D21">
-        <v>2.4001145362854</v>
+        <v>2.670837879180908</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1270,7 +1270,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>2.077150344848633</v>
+        <v>2.377763271331787</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D23">
-        <v>2.13360595703125</v>
+        <v>2.539760589599609</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>3.411724090576172</v>
+        <v>3.179505825042725</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D25">
-        <v>2.077685356140137</v>
+        <v>2.112305641174316</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D26">
-        <v>2.840991258621216</v>
+        <v>2.852127552032471</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1340,7 +1340,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>2.797869443893433</v>
+        <v>2.894580364227295</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>1.355161428451538</v>
+        <v>2.690036296844482</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D29">
-        <v>2.366057395935059</v>
+        <v>1.97846531867981</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1382,7 +1382,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D30">
-        <v>2.968175172805786</v>
+        <v>3.062873840332031</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1396,7 +1396,7 @@
         <v>1.5</v>
       </c>
       <c r="D31">
-        <v>3.120372772216797</v>
+        <v>3.242620229721069</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1410,7 +1410,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D32">
-        <v>3.618480443954468</v>
+        <v>3.057425022125244</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D33">
-        <v>2.661374568939209</v>
+        <v>2.820975780487061</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1438,7 +1438,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D34">
-        <v>3.837007522583008</v>
+        <v>3.316937923431396</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1452,7 +1452,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>3.923503637313843</v>
+        <v>3.110405206680298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D36">
-        <v>2.868787050247192</v>
+        <v>2.88555383682251</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1480,7 +1480,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D37">
-        <v>2.697478055953979</v>
+        <v>2.831936836242676</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1494,7 +1494,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D38">
-        <v>2.526055812835693</v>
+        <v>2.025523662567139</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1508,7 +1508,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D39">
-        <v>2.5465247631073</v>
+        <v>2.508666038513184</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1522,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>3.986955642700195</v>
+        <v>6.326048374176025</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1536,7 +1536,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D41">
-        <v>3.318404197692871</v>
+        <v>6.034749507904053</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1550,7 +1550,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>2.074422836303711</v>
+        <v>2.447047233581543</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1564,7 +1564,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D43">
-        <v>2.671916723251343</v>
+        <v>2.754461526870728</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1578,7 +1578,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D44">
-        <v>2.235946655273438</v>
+        <v>2.449310541152954</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1592,7 +1592,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D45">
-        <v>1.298978328704834</v>
+        <v>2.229994297027588</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1606,7 +1606,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D46">
-        <v>2.376072883605957</v>
+        <v>2.530838012695312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1620,7 +1620,7 @@
         <v>19.5</v>
       </c>
       <c r="D47">
-        <v>16.7632999420166</v>
+        <v>18.62347221374512</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1634,7 +1634,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D48">
-        <v>2.969971179962158</v>
+        <v>2.810181617736816</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D49">
-        <v>3.153878211975098</v>
+        <v>3.841570138931274</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1662,7 +1662,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D50">
-        <v>1.342620491981506</v>
+        <v>1.968541383743286</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1676,7 +1676,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D51">
-        <v>7.453809261322021</v>
+        <v>12.67637634277344</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1690,7 +1690,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D52">
-        <v>12.44902229309082</v>
+        <v>14.72379970550537</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1704,7 +1704,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D53">
-        <v>1.692232131958008</v>
+        <v>2.858855962753296</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1718,7 +1718,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D54">
-        <v>3.547892570495605</v>
+        <v>4.316762924194336</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1732,7 +1732,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D55">
-        <v>2.820774078369141</v>
+        <v>2.687255620956421</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1746,7 +1746,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D56">
-        <v>3.181339979171753</v>
+        <v>3.48507833480835</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1760,7 +1760,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D57">
-        <v>2.541733980178833</v>
+        <v>2.026569843292236</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1774,7 +1774,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D58">
-        <v>3.19219970703125</v>
+        <v>2.955331802368164</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1788,7 +1788,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.626777172088623</v>
+        <v>2.517330408096313</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1802,7 +1802,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D60">
-        <v>2.186969995498657</v>
+        <v>2.358940362930298</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1816,7 +1816,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D61">
-        <v>3.094094753265381</v>
+        <v>2.590425729751587</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1830,7 +1830,7 @@
         <v>1.5</v>
       </c>
       <c r="D62">
-        <v>1.851153612136841</v>
+        <v>2.459086894989014</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1844,7 +1844,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D63">
-        <v>3.236865520477295</v>
+        <v>2.820274591445923</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1858,7 +1858,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D64">
-        <v>4.948024272918701</v>
+        <v>10.81520843505859</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1872,7 +1872,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D65">
-        <v>3.253635883331299</v>
+        <v>3.497924327850342</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1886,7 +1886,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D66">
-        <v>2.703263521194458</v>
+        <v>2.839701890945435</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D67">
-        <v>1.99340033531189</v>
+        <v>2.439302921295166</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1914,7 +1914,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D68">
-        <v>4.280857086181641</v>
+        <v>3.733075141906738</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>1.358494877815247</v>
+        <v>3.093756675720215</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1942,7 +1942,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D70">
-        <v>10.83198928833008</v>
+        <v>13.59879875183105</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1956,7 +1956,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D71">
-        <v>2.993522644042969</v>
+        <v>2.944372653961182</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D72">
-        <v>1.550755262374878</v>
+        <v>2.434410095214844</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D73">
-        <v>3.489237308502197</v>
+        <v>3.631351470947266</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D74">
-        <v>3.041281223297119</v>
+        <v>3.129641056060791</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D75">
-        <v>1.683349370956421</v>
+        <v>2.327874898910522</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D76">
-        <v>2.785705804824829</v>
+        <v>2.821366548538208</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D77">
-        <v>2.791492938995361</v>
+        <v>2.902297258377075</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>3.491891622543335</v>
+        <v>3.893248558044434</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D79">
-        <v>2.565124750137329</v>
+        <v>2.513366460800171</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D80">
-        <v>3.583990335464478</v>
+        <v>4.057995319366455</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D81">
-        <v>3.524792671203613</v>
+        <v>3.451787948608398</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D82">
-        <v>2.42518949508667</v>
+        <v>2.608516454696655</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D83">
-        <v>3.504501104354858</v>
+        <v>3.320717811584473</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2138,7 +2138,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D84">
-        <v>3.121702194213867</v>
+        <v>2.990132331848145</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D85">
-        <v>5.615025520324707</v>
+        <v>5.709527969360352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D86">
-        <v>2.247764110565186</v>
+        <v>2.581188201904297</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2180,7 +2180,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D87">
-        <v>3.145695447921753</v>
+        <v>2.890040874481201</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D88">
-        <v>2.855453491210938</v>
+        <v>2.655993461608887</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D89">
-        <v>2.847634315490723</v>
+        <v>3.03061580657959</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D90">
-        <v>3.205344200134277</v>
+        <v>3.149601697921753</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D91">
-        <v>3.172804832458496</v>
+        <v>3.694332838058472</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D92">
-        <v>2.089817047119141</v>
+        <v>1.979780673980713</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>0.5</v>
       </c>
       <c r="D93">
-        <v>1.930773496627808</v>
+        <v>2.047537565231323</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D94">
-        <v>4.692911148071289</v>
+        <v>5.787126064300537</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D95">
-        <v>1.868629455566406</v>
+        <v>3.134740829467773</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="D96">
-        <v>1.420635223388672</v>
+        <v>2.348738670349121</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D97">
-        <v>2.133594274520874</v>
+        <v>2.059079885482788</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>2.012079238891602</v>
+        <v>1.497008323669434</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="D99">
-        <v>2.950982570648193</v>
+        <v>2.633795261383057</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D100">
-        <v>9.163732528686523</v>
+        <v>5.451595783233643</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2376,7 +2376,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D101">
-        <v>2.549255847930908</v>
+        <v>3.033116817474365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D102">
-        <v>3.12397575378418</v>
+        <v>3.266760110855103</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D103">
-        <v>3.931313037872314</v>
+        <v>5.799034118652344</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2418,7 +2418,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D104">
-        <v>3.97141170501709</v>
+        <v>3.195361137390137</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2432,7 +2432,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D105">
-        <v>2.79180908203125</v>
+        <v>2.919782161712646</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2446,7 +2446,7 @@
         <v>3</v>
       </c>
       <c r="D106">
-        <v>1.587036967277527</v>
+        <v>2.365700244903564</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D107">
-        <v>2.536765575408936</v>
+        <v>2.649247646331787</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D108">
-        <v>2.892442941665649</v>
+        <v>3.003427505493164</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2488,7 +2488,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>2.696149349212646</v>
+        <v>3.236594200134277</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>31</v>
       </c>
       <c r="D110">
-        <v>22.92305946350098</v>
+        <v>24.50704956054688</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2516,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="D111">
-        <v>2.992697954177856</v>
+        <v>4.031049251556396</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D112">
-        <v>10.55576610565186</v>
+        <v>16.46511650085449</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D113">
-        <v>3.499640941619873</v>
+        <v>4.227095127105713</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D114">
-        <v>2.21879243850708</v>
+        <v>2.516172170639038</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D115">
-        <v>2.502330303192139</v>
+        <v>2.805647373199463</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D116">
-        <v>3.846694946289062</v>
+        <v>4.745566844940186</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>1.705625295639038</v>
+        <v>2.816554546356201</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2614,7 +2614,7 @@
         <v>7.5</v>
       </c>
       <c r="D118">
-        <v>3.225844383239746</v>
+        <v>3.302520275115967</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D119">
-        <v>1.616744756698608</v>
+        <v>2.48645544052124</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>3.5</v>
       </c>
       <c r="D120">
-        <v>2.458795070648193</v>
+        <v>3.29126763343811</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D121">
-        <v>2.553224802017212</v>
+        <v>3.467356204986572</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2670,7 +2670,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D122">
-        <v>3.002611398696899</v>
+        <v>3.290499687194824</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D123">
-        <v>2.88396430015564</v>
+        <v>2.714883089065552</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>1.5</v>
       </c>
       <c r="D124">
-        <v>2.657671213150024</v>
+        <v>2.926445484161377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D125">
-        <v>3.095930576324463</v>
+        <v>3.491368770599365</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D126">
-        <v>2.739112377166748</v>
+        <v>2.65125560760498</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D127">
-        <v>6.874797344207764</v>
+        <v>10.55825710296631</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="D128">
-        <v>14.98371124267578</v>
+        <v>16.60149192810059</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D129">
-        <v>1.586054682731628</v>
+        <v>2.350637197494507</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D130">
-        <v>2.217604637145996</v>
+        <v>2.861752033233643</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D131">
-        <v>1.386576890945435</v>
+        <v>2.256948947906494</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2810,7 +2810,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D132">
-        <v>2.514478445053101</v>
+        <v>2.915263175964355</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D133">
-        <v>2.091150760650635</v>
+        <v>2.817168712615967</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D134">
-        <v>7.22875452041626</v>
+        <v>6.610562324523926</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D135">
-        <v>3.186002254486084</v>
+        <v>2.882266521453857</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D136">
-        <v>1.73063850402832</v>
+        <v>9.048666000366211</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D137">
-        <v>3.042486667633057</v>
+        <v>3.01446008682251</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D138">
-        <v>4.660854816436768</v>
+        <v>5.695968151092529</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2908,7 +2908,7 @@
         <v>32.20000076293945</v>
       </c>
       <c r="D139">
-        <v>23.31225395202637</v>
+        <v>24.99709701538086</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2922,7 +2922,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D140">
-        <v>2.656092643737793</v>
+        <v>3.209294080734253</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D141">
-        <v>4.053219318389893</v>
+        <v>5.316699981689453</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2950,7 +2950,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D142">
-        <v>2.846300601959229</v>
+        <v>2.828803777694702</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D143">
-        <v>1.636274099349976</v>
+        <v>3.084366321563721</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D144">
-        <v>1.402801036834717</v>
+        <v>3.639419555664062</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>1.897735834121704</v>
+        <v>1.281526565551758</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D146">
-        <v>17.84591865539551</v>
+        <v>22.61056137084961</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D147">
-        <v>2.827190637588501</v>
+        <v>2.451062202453613</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D148">
-        <v>1.895951747894287</v>
+        <v>2.363801717758179</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>2.954953670501709</v>
+        <v>2.693001270294189</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D150">
-        <v>1.367229461669922</v>
+        <v>2.82011604309082</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>5.5</v>
       </c>
       <c r="D151">
-        <v>1.368071794509888</v>
+        <v>2.390283107757568</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>2.625779390335083</v>
+        <v>2.711848020553589</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D153">
-        <v>2.473056077957153</v>
+        <v>2.593574523925781</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D154">
-        <v>4.396218299865723</v>
+        <v>4.784172058105469</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D155">
-        <v>2.437707901000977</v>
+        <v>2.535560607910156</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D156">
-        <v>3.904682397842407</v>
+        <v>3.461184740066528</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D157">
-        <v>8.179015159606934</v>
+        <v>9.459701538085938</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D158">
-        <v>1.450944423675537</v>
+        <v>1.42787504196167</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D159">
-        <v>1.446635246276855</v>
+        <v>1.702239274978638</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>3.5</v>
       </c>
       <c r="D160">
-        <v>2.975335121154785</v>
+        <v>2.899177074432373</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D161">
-        <v>2.676801919937134</v>
+        <v>2.86663293838501</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>3.5</v>
       </c>
       <c r="D162">
-        <v>2.598296880722046</v>
+        <v>2.629187107086182</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D163">
-        <v>2.443546772003174</v>
+        <v>2.098479986190796</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>1.5</v>
       </c>
       <c r="D164">
-        <v>2.150903224945068</v>
+        <v>2.748770713806152</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D165">
-        <v>17.6765251159668</v>
+        <v>20.34689140319824</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="D166">
-        <v>2.113515615463257</v>
+        <v>2.500499725341797</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>3.106755256652832</v>
+        <v>2.990174531936646</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D168">
-        <v>1.744463562965393</v>
+        <v>2.831891298294067</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D169">
-        <v>3.133358716964722</v>
+        <v>4.08128023147583</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D170">
-        <v>2.582894086837769</v>
+        <v>3.366847515106201</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D171">
-        <v>2.139276266098022</v>
+        <v>2.861513137817383</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D172">
-        <v>3.014128684997559</v>
+        <v>2.720144033432007</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>3.5</v>
       </c>
       <c r="D173">
-        <v>1.396958589553833</v>
+        <v>2.588028192520142</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D174">
-        <v>3.340382099151611</v>
+        <v>3.026146650314331</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>21.10000038146973</v>
       </c>
       <c r="D175">
-        <v>12.47060298919678</v>
+        <v>20.80824661254883</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3426,7 +3426,7 @@
         <v>5.5</v>
       </c>
       <c r="D176">
-        <v>3.000869750976562</v>
+        <v>2.964685678482056</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3440,7 +3440,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D177">
-        <v>2.456912279129028</v>
+        <v>3.03318452835083</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D178">
-        <v>1.414538383483887</v>
+        <v>1.643024444580078</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D179">
-        <v>3.25989556312561</v>
+        <v>3.390365839004517</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D180">
-        <v>3.065426826477051</v>
+        <v>3.149603843688965</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D181">
-        <v>1.340423822402954</v>
+        <v>1.913793325424194</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="D182">
-        <v>2.060367822647095</v>
+        <v>2.304814100265503</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D183">
-        <v>4.294051170349121</v>
+        <v>6.824082374572754</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D184">
-        <v>2.499980926513672</v>
+        <v>2.962120532989502</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3552,7 +3552,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D185">
-        <v>2.514397859573364</v>
+        <v>2.454827308654785</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3566,7 +3566,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D186">
-        <v>3.212121963500977</v>
+        <v>2.958929538726807</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>0.5</v>
       </c>
       <c r="D187">
-        <v>3.046627283096313</v>
+        <v>3.608709573745728</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3594,7 +3594,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>4.059493541717529</v>
+        <v>3.132018089294434</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D189">
-        <v>2.536785125732422</v>
+        <v>2.39030933380127</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D190">
-        <v>1.715467929840088</v>
+        <v>2.332968473434448</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D191">
-        <v>3.309592723846436</v>
+        <v>2.726212978363037</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3650,7 +3650,7 @@
         <v>5.5</v>
       </c>
       <c r="D192">
-        <v>4.327417850494385</v>
+        <v>3.723362684249878</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D193">
-        <v>2.185331583023071</v>
+        <v>2.506654024124146</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D194">
-        <v>2.677383899688721</v>
+        <v>2.804684638977051</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D195">
-        <v>3.175748348236084</v>
+        <v>3.399925470352173</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D196">
-        <v>3.824230670928955</v>
+        <v>3.98603630065918</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D197">
-        <v>4.164842128753662</v>
+        <v>6.783288478851318</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D198">
-        <v>2.870596885681152</v>
+        <v>2.905343532562256</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D199">
-        <v>2.113941431045532</v>
+        <v>2.433733463287354</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D200">
-        <v>2.515795707702637</v>
+        <v>2.760090112686157</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D201">
-        <v>1.965909242630005</v>
+        <v>2.45659351348877</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D202">
-        <v>20.00870323181152</v>
+        <v>19.58798217773438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D203">
-        <v>2.581514120101929</v>
+        <v>2.755207777023315</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D204">
-        <v>2.711763143539429</v>
+        <v>2.729903221130371</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D205">
-        <v>1.709531784057617</v>
+        <v>2.650711536407471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>20</v>
       </c>
       <c r="D206">
-        <v>12.78903198242188</v>
+        <v>13.76509284973145</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D207">
-        <v>1.58316969871521</v>
+        <v>2.790884256362915</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D208">
-        <v>2.639712333679199</v>
+        <v>2.151473760604858</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>2.5</v>
       </c>
       <c r="D209">
-        <v>1.516959309577942</v>
+        <v>2.286477088928223</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3902,7 +3902,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D210">
-        <v>2.336848735809326</v>
+        <v>2.632357835769653</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3916,7 +3916,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D211">
-        <v>4.24799919128418</v>
+        <v>4.358455657958984</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>3.880416870117188</v>
+        <v>3.558172702789307</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D213">
-        <v>7.304948806762695</v>
+        <v>10.3505916595459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D214">
-        <v>2.52451491355896</v>
+        <v>2.740070343017578</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D215">
-        <v>2.418818712234497</v>
+        <v>2.356466054916382</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3986,7 +3986,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D216">
-        <v>3.512568473815918</v>
+        <v>3.528928518295288</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4000,7 +4000,7 @@
         <v>4.5</v>
       </c>
       <c r="D217">
-        <v>5.162869930267334</v>
+        <v>4.685242176055908</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4014,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>2.136655569076538</v>
+        <v>2.086705207824707</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4028,7 +4028,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D219">
-        <v>2.054884433746338</v>
+        <v>2.378754377365112</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4042,7 +4042,7 @@
         <v>5</v>
       </c>
       <c r="D220">
-        <v>1.871942758560181</v>
+        <v>2.1998131275177</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4056,7 +4056,7 @@
         <v>2.5</v>
       </c>
       <c r="D221">
-        <v>3.073256015777588</v>
+        <v>3.005375385284424</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4070,7 +4070,7 @@
         <v>41</v>
       </c>
       <c r="D222">
-        <v>26.5783634185791</v>
+        <v>25.45269012451172</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4084,7 +4084,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D223">
-        <v>3.517411231994629</v>
+        <v>5.374135971069336</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4098,7 +4098,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D224">
-        <v>3.060209989547729</v>
+        <v>2.869831562042236</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D225">
-        <v>3.02445650100708</v>
+        <v>2.555258274078369</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4126,7 +4126,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D226">
-        <v>1.91122841835022</v>
+        <v>2.341650724411011</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4140,7 +4140,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D227">
-        <v>7.429773807525635</v>
+        <v>5.630187034606934</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4154,7 +4154,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D228">
-        <v>2.38280177116394</v>
+        <v>2.464228868484497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4168,7 +4168,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D229">
-        <v>3.419090509414673</v>
+        <v>3.222352504730225</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4182,7 +4182,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D230">
-        <v>2.05854320526123</v>
+        <v>2.22943115234375</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4196,7 +4196,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D231">
-        <v>3.256641864776611</v>
+        <v>3.912260055541992</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4210,7 +4210,7 @@
         <v>2.5</v>
       </c>
       <c r="D232">
-        <v>2.914349317550659</v>
+        <v>3.419192314147949</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4224,7 +4224,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D233">
-        <v>2.863654136657715</v>
+        <v>3.084665060043335</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4238,7 +4238,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D234">
-        <v>1.51506781578064</v>
+        <v>1.972956418991089</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4252,7 +4252,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D235">
-        <v>2.261242628097534</v>
+        <v>3.534890651702881</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4266,7 +4266,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D236">
-        <v>2.596815347671509</v>
+        <v>2.90827751159668</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4280,7 +4280,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D237">
-        <v>3.070768356323242</v>
+        <v>3.099353075027466</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4294,7 +4294,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D238">
-        <v>3.778043270111084</v>
+        <v>3.847614526748657</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4308,7 +4308,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D239">
-        <v>2.215075016021729</v>
+        <v>3.539850234985352</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4322,7 +4322,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D240">
-        <v>2.834458827972412</v>
+        <v>2.998593807220459</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4336,7 +4336,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D241">
-        <v>2.608854055404663</v>
+        <v>3.286032676696777</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4350,7 +4350,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D242">
-        <v>2.441785573959351</v>
+        <v>2.645062685012817</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4364,7 +4364,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D243">
-        <v>2.370137453079224</v>
+        <v>3.193151950836182</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4378,7 +4378,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D244">
-        <v>8.746049880981445</v>
+        <v>9.552042961120605</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4392,7 +4392,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D245">
-        <v>2.437990427017212</v>
+        <v>2.1517333984375</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4406,7 +4406,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D246">
-        <v>13.10758113861084</v>
+        <v>15.88737392425537</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4420,7 +4420,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D247">
-        <v>2.338412046432495</v>
+        <v>2.878135204315186</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4434,7 +4434,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D248">
-        <v>2.283738851547241</v>
+        <v>2.811995983123779</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4448,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="D249">
-        <v>1.366079807281494</v>
+        <v>2.510936260223389</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4462,7 +4462,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D250">
-        <v>2.879703998565674</v>
+        <v>2.191861152648926</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4476,7 +4476,7 @@
         <v>3.5</v>
       </c>
       <c r="D251">
-        <v>3.173774719238281</v>
+        <v>4.621035099029541</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4490,7 +4490,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D252">
-        <v>2.469763517379761</v>
+        <v>2.612036466598511</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4504,7 +4504,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D253">
-        <v>2.897017478942871</v>
+        <v>2.863030672073364</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4518,7 +4518,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D254">
-        <v>17.35650444030762</v>
+        <v>13.30076885223389</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4532,7 +4532,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D255">
-        <v>26.07735824584961</v>
+        <v>30.56356811523438</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4546,7 +4546,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D256">
-        <v>2.02656888961792</v>
+        <v>3.186749458312988</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4560,7 +4560,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D257">
-        <v>2.240460157394409</v>
+        <v>2.606687784194946</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4574,7 +4574,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>1.89959192276001</v>
+        <v>2.260976314544678</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4588,7 +4588,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D259">
-        <v>3.092042922973633</v>
+        <v>3.045333862304688</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4602,7 +4602,7 @@
         <v>16.5</v>
       </c>
       <c r="D260">
-        <v>3.015645027160645</v>
+        <v>3.186330318450928</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4616,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="D261">
-        <v>2.226178884506226</v>
+        <v>2.397849798202515</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4630,7 +4630,7 @@
         <v>6</v>
       </c>
       <c r="D262">
-        <v>3.359698295593262</v>
+        <v>3.227862119674683</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4644,7 +4644,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D263">
-        <v>3.842691421508789</v>
+        <v>4.699223041534424</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4658,7 +4658,7 @@
         <v>3.5</v>
       </c>
       <c r="D264">
-        <v>2.22546648979187</v>
+        <v>2.317371845245361</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4672,7 +4672,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D265">
-        <v>1.786256790161133</v>
+        <v>2.298068046569824</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4686,7 +4686,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D266">
-        <v>2.961469173431396</v>
+        <v>2.497594833374023</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4700,7 +4700,7 @@
         <v>5.5</v>
       </c>
       <c r="D267">
-        <v>2.250399827957153</v>
+        <v>2.765883445739746</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4714,7 +4714,7 @@
         <v>29.20000076293945</v>
       </c>
       <c r="D268">
-        <v>21.71986961364746</v>
+        <v>27.87699508666992</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4728,7 +4728,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D269">
-        <v>2.689096212387085</v>
+        <v>3.309263229370117</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4742,7 +4742,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D270">
-        <v>3.121386051177979</v>
+        <v>3.074156761169434</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4756,7 +4756,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D271">
-        <v>2.391097068786621</v>
+        <v>2.19619083404541</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4770,7 +4770,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D272">
-        <v>6.155924320220947</v>
+        <v>8.759686470031738</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4784,7 +4784,7 @@
         <v>7.5</v>
       </c>
       <c r="D273">
-        <v>9.260440826416016</v>
+        <v>12.60216331481934</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4798,7 +4798,7 @@
         <v>3</v>
       </c>
       <c r="D274">
-        <v>3.082435607910156</v>
+        <v>3.189221143722534</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4812,7 +4812,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D275">
-        <v>3.153887748718262</v>
+        <v>2.81791090965271</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4826,7 +4826,7 @@
         <v>3.5</v>
       </c>
       <c r="D276">
-        <v>2.420794486999512</v>
+        <v>2.854747533798218</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4840,7 +4840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D277">
-        <v>2.25130295753479</v>
+        <v>3.092995166778564</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4854,7 +4854,7 @@
         <v>3.5</v>
       </c>
       <c r="D278">
-        <v>2.057439804077148</v>
+        <v>2.169376373291016</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4868,7 +4868,7 @@
         <v>31.29999923706055</v>
       </c>
       <c r="D279">
-        <v>25.04685592651367</v>
+        <v>24.39018821716309</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4882,7 +4882,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D280">
-        <v>1.355025053024292</v>
+        <v>2.632890462875366</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4896,7 +4896,7 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>1.591687321662903</v>
+        <v>2.931848526000977</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>3.351202249526978</v>
+        <v>3.173365354537964</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4924,7 +4924,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D283">
-        <v>1.767292976379395</v>
+        <v>1.986891508102417</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4938,7 +4938,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D284">
-        <v>2.755057811737061</v>
+        <v>2.688335418701172</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4952,7 +4952,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>2.762711524963379</v>
+        <v>2.677294969558716</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4966,7 +4966,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D286">
-        <v>1.625918626785278</v>
+        <v>2.618037939071655</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4980,7 +4980,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D287">
-        <v>3.206795692443848</v>
+        <v>3.376416683197021</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4994,7 +4994,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>2.705237150192261</v>
+        <v>2.955778121948242</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5008,7 +5008,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D289">
-        <v>1.796899080276489</v>
+        <v>2.183197259902954</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5022,7 +5022,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D290">
-        <v>2.730422019958496</v>
+        <v>2.892379760742188</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5036,7 +5036,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D291">
-        <v>2.061615705490112</v>
+        <v>2.002869129180908</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5050,7 +5050,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D292">
-        <v>3.291150093078613</v>
+        <v>3.097491264343262</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5064,7 +5064,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>2.748396635055542</v>
+        <v>3.03803825378418</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5078,7 +5078,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D294">
-        <v>8.605456352233887</v>
+        <v>14.80212593078613</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5092,7 +5092,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D295">
-        <v>2.637854814529419</v>
+        <v>2.473318815231323</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5106,7 +5106,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D296">
-        <v>2.965601205825806</v>
+        <v>3.06298041343689</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5120,7 +5120,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D297">
-        <v>3.819424629211426</v>
+        <v>3.660380363464355</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5134,7 +5134,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D298">
-        <v>2.097911357879639</v>
+        <v>2.767772197723389</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5148,7 +5148,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D299">
-        <v>2.619376659393311</v>
+        <v>2.725422859191895</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5162,7 +5162,7 @@
         <v>30.5</v>
       </c>
       <c r="D300">
-        <v>15.63920783996582</v>
+        <v>18.92369842529297</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5176,7 +5176,7 @@
         <v>4.5</v>
       </c>
       <c r="D301">
-        <v>2.862039804458618</v>
+        <v>2.589812517166138</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5190,7 +5190,7 @@
         <v>5</v>
       </c>
       <c r="D302">
-        <v>2.51891016960144</v>
+        <v>1.98206639289856</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5204,7 +5204,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D303">
-        <v>20.60543441772461</v>
+        <v>26.49132537841797</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5218,7 +5218,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D304">
-        <v>2.600985765457153</v>
+        <v>2.88519287109375</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5232,7 +5232,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D305">
-        <v>2.498030185699463</v>
+        <v>3.226502656936646</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5246,7 +5246,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>2.035036563873291</v>
+        <v>2.513099193572998</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5260,7 +5260,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D307">
-        <v>3.483866930007935</v>
+        <v>3.876831531524658</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5274,7 +5274,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D308">
-        <v>2.401302337646484</v>
+        <v>2.628378391265869</v>
       </c>
     </row>
   </sheetData>
